--- a/artfynd/A 28304-2021 artfynd.xlsx
+++ b/artfynd/A 28304-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28304-2021 artfynd.xlsx
+++ b/artfynd/A 28304-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1636,113 +1636,6 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>112606750</v>
-      </c>
-      <c r="B10" t="n">
-        <v>89791</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Björnhult, Sm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>579578</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6351146</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Oskarshamn</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Döderhult</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
